--- a/samples/ss_cirata_ingest.xlsx
+++ b/samples/ss_cirata_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,7 +611,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GITET Cirata 1,2</t>
+          <t>GITET Cirata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CRATA5_12</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CRATA5_12</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -806,33 +806,51 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GITET Cirata 3</t>
+          <t>IBT 3 Cirata 500/150 kV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRAT37</t>
+          <t>IBT 3 CRATA7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>500 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CRATA7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CRATA5_3</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1 IBT (unit 3)</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -859,49 +877,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IBT 3 Cirata 500/150 kV</t>
+          <t>Cirata 1,2 (bus 150 kV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IBT 3 CRAT37</t>
+          <t>CRATA5_12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CRAT37</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CRATA5</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1 IBT (unit 3)</t>
+          <t>bus section 1,2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -930,12 +934,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cirata (bus 150 kV)</t>
+          <t>Cirata 3 (bus 150 kV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CRATA5_3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -958,7 +962,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>bus section + kopel</t>
+          <t>bus section 3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jatiluhur</t>
+          <t>Jatiluhur (bus 150 kV)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1260,17 +1264,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lengkong Dar</t>
+          <t>Trafo 1 Jatiluhur 150/70 kV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LGDAR</t>
+          <t>TRF 1 JTLHR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1278,19 +1282,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>JTLHR</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>JTLHR4</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1317,17 +1331,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Padalarang Baru</t>
+          <t>Trafo 2 Jatiluhur 150/70 kV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PDLRU</t>
+          <t>TRF 2 JTLHR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1335,13 +1349,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>JTLHR</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JTLHR4</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1353,14 +1381,10 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1374,17 +1398,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cikampek</t>
+          <t>Trafo 3 Jatiluhur 150/70 kV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CKMPY</t>
+          <t>TRF 3 JTLHR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1392,13 +1416,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>JTLHR</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JTLHR4</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1427,12 +1465,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Purwakarta (bus 150 kV)</t>
+          <t>Jatiluhur (bus 70 kV)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PWKTA</t>
+          <t>JTLHR4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1445,7 +1483,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1463,14 +1501,10 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1484,17 +1518,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Cirata</t>
+          <t>Lengkong Dar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IBT 1 CRATA5</t>
+          <t>LGDAR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1502,31 +1536,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>CRATA5</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CRATA4</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV</t>
+          <t>bus section + kopel</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1538,14 +1558,10 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1559,12 +1575,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cirata (bus 70 kV)</t>
+          <t>Padalarang Baru</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CRATA4</t>
+          <t>PDLRU</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1577,7 +1593,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1600,7 +1616,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1616,12 +1632,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bandung Utara</t>
+          <t>Cikampek</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BDUTR</t>
+          <t>CKMPY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1630,7 +1646,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1669,12 +1685,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cibabat Baru</t>
+          <t>Purwakarta (bus 150 kV)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CBBRU</t>
+          <t>PWKTA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1683,7 +1699,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1710,7 +1726,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1726,33 +1742,51 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cibabat</t>
+          <t>IBT 150/70 kV Cirata</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CBBAT</t>
+          <t>IBT 1 CRATA5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CRATA5_12</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CRATA4</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -1762,10 +1796,14 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1779,12 +1817,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indramayu (bus 150 kV)</t>
+          <t>Cirata (bus 70 kV)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IDRMA5</t>
+          <t>CRATA4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1793,11 +1831,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1815,10 +1853,14 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1832,12 +1874,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pabuaran</t>
+          <t>Bandung Utara</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PBRAN</t>
+          <t>BDUTR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1885,12 +1927,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Degung Pakar</t>
+          <t>Cibabat Baru</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DGPKR</t>
+          <t>CBBRU</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1899,7 +1941,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1921,10 +1963,14 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1938,17 +1984,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Purwakarta</t>
+          <t>Cibabat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IBT 1 PWKTA</t>
+          <t>CBBAT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1956,33 +2002,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>PWKTA</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>PWKTA4</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -2009,12 +2037,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Purwakarta (bus 70 kV)</t>
+          <t>Indramayu (bus 150 kV)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PWKTA4</t>
+          <t>IDRMA5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2027,7 +2055,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2062,12 +2090,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indramayu (bus 70 kV)</t>
+          <t>Pabuaran</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IDRMA</t>
+          <t>PBRAN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2076,11 +2104,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2098,14 +2126,10 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2119,12 +2143,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sipfic</t>
+          <t>Degung Pakar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SPFIC</t>
+          <t>DGPKR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2137,7 +2161,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -2155,14 +2179,10 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2176,33 +2196,51 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kosambi Baru</t>
+          <t>Trafo 1 Purwakarta 150/70 kV</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KSBRU</t>
+          <t>IBT 1 PWKTA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PWKTA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PWKTA4</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Trafo 150/70 kV</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
@@ -2212,14 +2250,10 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2233,33 +2267,51 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>Trafo 2 Purwakarta 150/70 kV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SBANG</t>
+          <t>IBT 2 PWKTA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PWKTA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PWKTA4</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Trafo 150/70 kV</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
@@ -2269,14 +2321,10 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2290,12 +2338,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Indocement</t>
+          <t>Purwakarta (bus 70 kV)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INDCI</t>
+          <t>PWKTA4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2304,7 +2352,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2343,12 +2391,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cigunea</t>
+          <t>Indramayu (bus 70 kV)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CGNEA</t>
+          <t>IDRMA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2357,7 +2405,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2379,10 +2427,14 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2396,12 +2448,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Indramayu Barat</t>
+          <t>Sipfic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IDBRT</t>
+          <t>SPFIC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2410,7 +2462,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2432,10 +2484,14 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2449,12 +2505,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Curug</t>
+          <t>Kosambi Baru</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CURUG</t>
+          <t>KSBRU</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2463,7 +2519,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2485,10 +2541,14 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2502,12 +2562,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tegal Tanjung Baru (SS Cibatu 3,4)</t>
+          <t>Subang</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TTJBR</t>
+          <t>SBANG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2516,11 +2576,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2528,28 +2588,24 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2563,12 +2619,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pondok Ali (SS Cibatu 3,4)</t>
+          <t>Indocement</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PNDLI</t>
+          <t>INDCI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2589,22 +2645,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2624,12 +2672,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rendeh Salak (SS Cibatu 3,4)</t>
+          <t>Cigunea</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RDSLK</t>
+          <t>CGNEA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2650,22 +2698,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2685,12 +2725,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cigereleng (SS Bandung Selatan)</t>
+          <t>Indramayu Barat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CGRLG</t>
+          <t>IDBRT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2699,11 +2739,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2711,22 +2751,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
-        </is>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2746,12 +2778,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ujung Berung (SS Bandung Selatan)</t>
+          <t>Curug</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>CURUG</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2764,7 +2796,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2772,22 +2804,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2800,6 +2824,311 @@
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tegal Tanjung Baru (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TTJBR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pondok Ali (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PNDLI</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rendeh Salak (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>RDSLK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cigereleng (SS Bandung Selatan)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CGRLG</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ujung Berung (SS Bandung Selatan)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UBRNG</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2812,7 +3141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,7 +3366,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CRATA5_12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3086,7 +3415,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SUTT Purwakarta - Cirata</t>
+          <t>SUTT Purwakarta - Cirata 1,2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3096,7 +3425,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CRATA5_12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3142,24 +3471,20 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SUTT Jatiluhur - Cirata</t>
+          <t>SUTT Purwakarta - Lengkong Dar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JTLHR</t>
+          <t>PTUHA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>LGDAR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3178,7 +3503,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -3192,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -3208,17 +3533,17 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUTT Purwakarta - Lengkong Dar</t>
+          <t>SUTT Jatiluhur - Tegal Tanjung Baru (arah SS Cibatu 3,4)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PTUHA</t>
+          <t>JTLHR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LGDAR</t>
+          <t>TTJBR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3264,20 +3589,24 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUTT Jatiluhur - Tegal Tanjung Baru (arah SS Cibatu 3,4)</t>
+          <t>SUTT Cirata 1,2 - Padalarang Baru</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JTLHR</t>
+          <t>CRATA5_12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TTJBR</t>
+          <t>PDLRU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3296,7 +3625,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -3323,24 +3652,20 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUTT Cirata - Padalarang Baru</t>
+          <t>SUTT Cirata 1,2 - Cikampek</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CRATA5_12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PDLRU</t>
+          <t>CKMPY</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3359,7 +3684,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -3386,20 +3711,24 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUTT Cirata - Cikampek</t>
+          <t>SUTT Cirata 3 - Purwakarta</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CRATA5_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CKMPY</t>
+          <t>PWKTA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3418,7 +3747,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -3445,19 +3774,15 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUTT Cirata - Purwakarta</t>
+          <t>SUTT Cikampek - Purwakarta single phi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRATA5</t>
+          <t>CKMPY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3472,7 +3797,7 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3481,7 +3806,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -3492,14 +3817,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -4593,17 +4918,17 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUTT 70 kV Cirata - Subang</t>
+          <t>SUTT 70 kV Jatiluhur - Ciganea</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRATA4</t>
+          <t>JTLHR4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SBANG</t>
+          <t>CGNEA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4636,7 +4961,7 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -4644,6 +4969,124 @@
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SUTT 70 kV Jatiluhur - Curug</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JTLHR4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CURUG</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SUTT 70 kV Cirata - Purwakarta</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRATA4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PWKTA4</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_cirata_ingest.xlsx
+++ b/samples/ss_cirata_ingest.xlsx
@@ -632,31 +632,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -703,15 +693,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -727,7 +713,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -774,15 +759,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -798,7 +779,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -845,31 +825,26 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>1 IBT (unit 3)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -898,35 +873,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>bus section 1,2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -955,35 +921,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>bus section 3</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1012,31 +969,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1065,19 +1012,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1093,7 +1032,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1122,31 +1060,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1175,31 +1103,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1228,19 +1146,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1256,7 +1166,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1303,27 +1212,21 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1370,27 +1273,21 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1437,27 +1334,21 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1486,31 +1377,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1539,35 +1420,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1596,19 +1468,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1624,7 +1488,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1653,31 +1516,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1706,19 +1559,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1734,7 +1579,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1781,19 +1625,16 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1809,7 +1650,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1838,19 +1678,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1866,7 +1698,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1895,31 +1726,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1948,19 +1769,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1976,7 +1789,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2005,31 +1817,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2058,31 +1860,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2111,31 +1903,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2164,31 +1946,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2235,31 +2007,26 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>Trafo 150/70 kV</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2306,31 +2073,26 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>Trafo 150/70 kV</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2359,31 +2121,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2412,19 +2164,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2440,7 +2184,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2469,19 +2212,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2497,7 +2232,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2526,19 +2260,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2554,7 +2280,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2583,19 +2308,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2611,7 +2328,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2640,31 +2356,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2693,31 +2399,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2746,31 +2442,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2799,31 +2485,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2852,17 +2528,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2878,13 +2548,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2913,17 +2581,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2939,13 +2601,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2974,17 +2634,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3000,13 +2654,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3035,17 +2687,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3061,13 +2707,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3096,17 +2740,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3122,13 +2760,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3235,7 +2871,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTA Cirata</t>
@@ -3256,7 +2891,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -3270,8 +2904,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3288,13 +2920,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTA Jatiluhur</t>
@@ -3315,7 +2945,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -3329,8 +2958,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3347,13 +2974,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Outlet PLTS Cirata</t>
@@ -3374,7 +2999,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -3388,8 +3012,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3406,13 +3028,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTT Purwakarta - Cirata 1,2</t>
@@ -3433,7 +3053,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -3447,8 +3066,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3465,13 +3082,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Purwakarta - Lengkong Dar</t>
@@ -3492,7 +3107,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -3506,8 +3120,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3524,13 +3136,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Jatiluhur - Tegal Tanjung Baru (arah SS Cibatu 3,4)</t>
@@ -3551,7 +3161,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -3565,8 +3174,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3583,7 +3190,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3614,7 +3220,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -3628,8 +3233,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3646,13 +3249,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Cirata 1,2 - Cikampek</t>
@@ -3673,7 +3274,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -3687,8 +3287,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3705,7 +3303,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3736,7 +3333,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -3750,8 +3346,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3768,13 +3362,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT Cikampek - Purwakarta single phi</t>
@@ -3795,7 +3387,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -3809,8 +3400,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3827,13 +3416,11 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Lengkong Dar - Cigereleng (arah SS Bandung Selatan)</t>
@@ -3854,7 +3441,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -3868,8 +3454,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3886,13 +3470,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Padalarang Baru - Bandung Utara</t>
@@ -3913,7 +3495,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -3927,8 +3508,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3945,7 +3524,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3976,7 +3554,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -3990,8 +3567,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4008,13 +3583,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Cikampek - Cibabat</t>
@@ -4035,7 +3608,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -4049,8 +3621,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4067,13 +3637,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>SUTT Cikampek - Indramayu</t>
@@ -4094,7 +3662,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -4108,8 +3675,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4126,13 +3691,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Cikampek - Pabuaran</t>
@@ -4153,7 +3716,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -4167,8 +3729,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4185,13 +3745,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT Bandung Utara - Degung Pakar</t>
@@ -4212,7 +3770,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -4226,8 +3783,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4244,13 +3799,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT Degung Pakar - Ujung Berung (arah SS Bandung Selatan)</t>
@@ -4271,7 +3824,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -4285,8 +3837,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4303,7 +3853,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4334,7 +3883,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1</v>
       </c>
@@ -4348,8 +3896,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4366,7 +3912,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4397,7 +3942,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -4411,8 +3955,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4429,7 +3971,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4460,7 +4001,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -4474,8 +4014,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4492,7 +4030,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4523,7 +4060,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -4537,8 +4073,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4555,13 +4089,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT 70 kV Indramayu - Indocement</t>
@@ -4582,7 +4114,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -4596,8 +4127,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4614,13 +4143,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>SUTT 70 kV Sipfic - Cigunea</t>
@@ -4641,7 +4168,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -4655,8 +4181,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4673,13 +4197,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTT 70 kV Kosambi Baru - Indramayu Barat</t>
@@ -4700,7 +4222,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -4714,8 +4235,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4732,13 +4251,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>SUTT 70 kV Kosambi Baru - Curug</t>
@@ -4759,7 +4276,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -4773,8 +4289,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4791,13 +4305,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>SUTT 70 kV Kosambi Baru - Pondok Ali (arah SS Cibatu 3,4)</t>
@@ -4818,7 +4330,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -4832,8 +4343,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4850,13 +4359,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>SUTT 70 kV Kosambi Baru - Rendeh Salak (arah SS Cibatu 3,4)</t>
@@ -4877,7 +4384,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -4891,8 +4397,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4909,13 +4413,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>SUTT 70 kV Jatiluhur - Ciganea</t>
@@ -4936,7 +4438,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -4950,8 +4451,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4968,13 +4467,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>SUTT 70 kV Jatiluhur - Curug</t>
@@ -4995,7 +4492,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -5009,8 +4505,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5027,13 +4521,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>SUTT 70 kV Cirata - Purwakarta</t>
@@ -5054,7 +4546,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -5068,8 +4559,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5086,7 +4575,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5191,8 +4679,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5231,8 +4717,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5271,8 +4755,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5311,8 +4793,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5351,8 +4831,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5471,7 +4949,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan Kopel GI Jatiluhur (GI Jatiluhur milik Perum Jasa Tirta). Update : Kopel sudah selesai, namun terkendala sertifikasi &amp; komisioning (Perlu bantuan PLN, UP2B Jabar akan bersurat ke GM UIP2B JAMALI dan PJT Pusat untuk percepatan sertifikasi dan komisioning). 2. Pembangunan GI 150 kV Jatiluhur Baru, sesuai RUPTL 2025-2034, COD 2025</t>
+          <t>Jangka Pendek: 1. Pembangunan Kopel GI Jatiluhur (GI Jatiluhur milik Perum Jasa Tirta). Update : Kopel sudah selesai, namun terkendala sertifikasi &amp; komisioning (Perlu bantuan PLN, UP2B Jabar akan bersurat ke GM UIP2B JAMALI dan PJT Pusat untuk percepatan sertifikasi dan komisioning). 2. Pembangunan GI 150 kV Jatiluhur Baru, sesuai RUPTL 2025 -2034, COD 2025</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5019,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Percepatan pembangunan GI 150 kV Subang Baru (memotong SUTT SKMDI-HRGLS 1,2), sehingga beban GI 70 kV Subang dapat dipindah sebagian ke GI 150 kV Subang Baru. Sesuai RUPTL 2025-2034, COD 2025. (sudah terkontrak efektif pada 14 Mar 2023)</t>
+          <t>Jangka Pendek: Percepatan pembangunan GI 150 kV Subang Baru (memotong SUTT SKMDI-HRGLS 1,2), sehingga beban GI 70 kV Subang dapat dipindah sebagian ke GI 150 kV Subang Baru. Sesuai RUPTL 2025 -2034, COD 2025. (sudah terkontrak efektif pada 14 Mar 2023)</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5039,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Padalarang Baru-Bandung Utara sudah di atas 60% (@63%, N-1 Tidak terpenuhi), Ketika memasok GI 150 kV Bandung Utara dan GI 150 kV Dagopakar</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Padalarang Baru -Bandung Utara sudah di atas 60% (@63%, N-1 Tidak terpenuhi), Ketika memasok GI 150 kV Bandung Utara dan GI 150 kV Dagopakar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5571,12 +5049,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1. Telah Terpasang OLS di SUTT 150 kV Padalarang-Bandung Utara dengan total target sebesar 74 MW. 2. Rekonfigurasi Jaringan/beban ke SS BDSLN-NUBRG</t>
+          <t>1. Telah Terpasang OLS di SUTT 150 kV Padalarang -Bandung Utara dengan total target sebesar 74 MW. 2. Rekonfigurasi Jaringan/beban ke SS BDSLN-NUBRG</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Rekonduktoring SUTT 150 kV Padalarang - Bandung Utara, sesuai RUPTL 2025-2034, COD 2027</t>
+          <t>Jangka Pendek: Rekonduktoring SUTT 150 kV Padalarang - Bandung Utara, sesuai RUPTL 2025 -2034, COD 2027</t>
         </is>
       </c>
     </row>
